--- a/workspace/framework_paper/edf/edf-15/edf-15_times_success.xlsx
+++ b/workspace/framework_paper/edf/edf-15/edf-15_times_success.xlsx
@@ -438,13 +438,13 @@
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.004475654908455909</v>
+        <v>0.0034768399852328</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009180180933326483</v>
+        <v>0.00828864841721952</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09187103460077196</v>
+        <v>0.005314134154468774</v>
       </c>
     </row>
     <row r="3">
@@ -452,13 +452,13 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.005556176693644375</v>
+        <v>0.003711785834748298</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009035609131678939</v>
+        <v>0.008099118401296436</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1282619577180594</v>
+        <v>0.006118130744434893</v>
       </c>
     </row>
     <row r="4">
@@ -466,13 +466,13 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.005725494166836142</v>
+        <v>0.00462902499595657</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0102996817138046</v>
+        <v>0.009029241669923067</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2081459870934486</v>
+        <v>0.005910758380778134</v>
       </c>
     </row>
     <row r="5">
@@ -480,13 +480,13 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.006258653218392283</v>
+        <v>0.005055269966833293</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01136325403116643</v>
+        <v>0.0102256665751338</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7434909703582525</v>
+        <v>0.007199408253654838</v>
       </c>
     </row>
     <row r="6">
@@ -494,13 +494,13 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.005789717114431427</v>
+        <v>0.005122383927649006</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05014950239099562</v>
+        <v>0.04800986477173865</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4351918746251613</v>
+        <v>0.2058267559064552</v>
       </c>
     </row>
     <row r="7">
@@ -508,13 +508,13 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.00672010902037963</v>
+        <v>0.006251522136772884</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03278936648133154</v>
+        <v>0.02799111308187854</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6410179621167481</v>
+        <v>0.04139015621505678</v>
       </c>
     </row>
     <row r="8">
@@ -522,13 +522,13 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.007278494645861235</v>
+        <v>0.007095643576789409</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01550314494913133</v>
+        <v>0.01530702940848035</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7143888735771179</v>
+        <v>0.05211552135646343</v>
       </c>
     </row>
     <row r="9">
@@ -536,13 +536,13 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0.007679806085829826</v>
+        <v>0.008022723820708368</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02056623790607167</v>
+        <v>0.01915682130493224</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9128986129257828</v>
+        <v>0.1055964924953878</v>
       </c>
     </row>
     <row r="10">
@@ -550,13 +550,13 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0.009429990971946845</v>
+        <v>0.009454427524874716</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02404850967771684</v>
+        <v>0.0227255648933351</v>
       </c>
       <c r="D10" t="n">
-        <v>1.534199603740126</v>
+        <v>0.1086060121562332</v>
       </c>
     </row>
     <row r="11">
@@ -564,13 +564,13 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01068892342384991</v>
+        <v>0.01012662797083342</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03154900085064583</v>
+        <v>0.03055572129475574</v>
       </c>
       <c r="D11" t="n">
-        <v>1.848337378762662</v>
+        <v>0.2043951051775366</v>
       </c>
     </row>
     <row r="12">
@@ -578,13 +578,13 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01108805302064866</v>
+        <v>0.01011032912647352</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05475246470693188</v>
+        <v>0.05268982111980828</v>
       </c>
       <c r="D12" t="n">
-        <v>2.405230891149567</v>
+        <v>0.3368364319577813</v>
       </c>
     </row>
     <row r="13">
@@ -592,13 +592,13 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01285541236687165</v>
+        <v>0.01308238681835624</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05920211742024706</v>
+        <v>0.05736630232802228</v>
       </c>
       <c r="D13" t="n">
-        <v>3.414147976709872</v>
+        <v>1.00447624287568</v>
       </c>
     </row>
     <row r="14">
@@ -606,13 +606,13 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01488162248278968</v>
+        <v>0.01405516023805831</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1608576887064492</v>
+        <v>0.1556058560558797</v>
       </c>
       <c r="D14" t="n">
-        <v>5.142222117404549</v>
+        <v>1.576620513240674</v>
       </c>
     </row>
     <row r="15">
@@ -620,13 +620,13 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>0.05499968966168742</v>
+        <v>0.05508923260945706</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3072018353051917</v>
+        <v>0.2973447400903286</v>
       </c>
       <c r="D15" t="n">
-        <v>9.221850644797087</v>
+        <v>5.142844013324839</v>
       </c>
     </row>
     <row r="16">
@@ -634,13 +634,13 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>0.02051434422739678</v>
+        <v>0.02021631325974509</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4721651090774685</v>
+        <v>0.465272352239117</v>
       </c>
       <c r="D16" t="n">
-        <v>11.60403181206096</v>
+        <v>3.946646545744604</v>
       </c>
     </row>
     <row r="17">
@@ -648,13 +648,13 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01816843204984539</v>
+        <v>0.01795062045321653</v>
       </c>
       <c r="C17" t="n">
-        <v>2.248877540541192</v>
+        <v>2.199060738764026</v>
       </c>
       <c r="D17" t="n">
-        <v>16.88729225234552</v>
+        <v>6.142949038003458</v>
       </c>
     </row>
     <row r="18">
@@ -662,13 +662,13 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>0.02183432476595044</v>
+        <v>0.02350726649165153</v>
       </c>
       <c r="C18" t="n">
-        <v>1.873613233107232</v>
+        <v>1.901023467221568</v>
       </c>
       <c r="D18" t="n">
-        <v>22.82034344245226</v>
+        <v>12.32247831023021</v>
       </c>
     </row>
     <row r="19">
@@ -676,13 +676,13 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0.02616706812246279</v>
+        <v>0.02782043628394604</v>
       </c>
       <c r="C19" t="n">
-        <v>1.246021021433451</v>
+        <v>1.244587781459645</v>
       </c>
       <c r="D19" t="n">
-        <v>93.07534859521049</v>
+        <v>28.99110988879035</v>
       </c>
     </row>
     <row r="20">
@@ -690,13 +690,13 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0.05025994898751378</v>
+        <v>0.05033552488312125</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1992018569849039</v>
+        <v>0.2031915168228902</v>
       </c>
       <c r="D20" t="n">
-        <v>61.17193862163659</v>
+        <v>27.7255254417037</v>
       </c>
     </row>
     <row r="21">
@@ -704,13 +704,13 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0384000555301706</v>
+        <v>0.03629668119053046</v>
       </c>
       <c r="C21" t="n">
-        <v>5.563458015909418</v>
+        <v>5.57977552851662</v>
       </c>
       <c r="D21" t="n">
-        <v>96.46395353648974</v>
+        <v>34.26040785573423</v>
       </c>
     </row>
   </sheetData>
